--- a/paper/source_data/ed3_source_data.xlsx
+++ b/paper/source_data/ed3_source_data.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256.</t>
+          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256, with one further column pair for each further file a row was read from.</t>
         </is>
       </c>
     </row>
@@ -497,13 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>**Extended Data Fig. 3 | Representation comparison details.** Companion to Fig. 3, with the same 26 conditions and 1,928 AI-READI development participants.
-**a**, Native heads through three routes. Top, macro AUROC. Bottom, per-condition gain from adding the retina to clinical data and clinical data to the retina. #, condition that may be defined from an encoder input.
-**b**, BRAN combined minus each of 13 arms per condition under one fixed logistic readout (C = 1). Wins and losses, 95% intervals excluding zero.
-**c**, The 14 arms of that readout, with inputs, macro AUROC and BRAN combined minus each arm. Ticks, one-sided Bonferroni bounds over five prespecified comparators.
-**d**, BRAN combined minus three arms under four readouts (¶, earlier label-free encoder), and eye-alone AUROC from an earlier benchmark (§, point estimates) beside tuned eye-alone contrasts.
-**e**, Paired differences after refitting the fixed readout on 25 to 100% of training labels.
-Points, estimates. Bars, 95% within-fold participant bootstrap intervals (1,000 draws). Per-condition intervals are unadjusted. Adverse results. BRAN combined did not exceed its clinical route, blood tests plus age or raw clinical values plus age (**c**) and lost 7, 6 and 7 conditions to them (**b**). Adding the retina lowered heart-attack detection (**a**). The label-free encoder only tied raw concatenation with a tuned logistic readout and lost to ExtraTrees (**d**). The BRAN retinal route trailed retinal foundation models (**d**). The clinical route beat BRAN combined with 50% and 75% of labels, and raw clinical values plus age beat it with 75% and scored higher at every budget (**e**). Under per-arm tuning the 125 wins and 0 losses against eight foundation-model arms became 76 wins and 16 losses (Fig. 3d). No panel is external validation, RETFound-Green is not the original RETFound, and a Labrador cache discrepancy of up to 0.0054 AUROC per condition is unresolved. Intervals for the mean rows of **b** and the 22-condition mean of **a** are PLACEHOLDER.</t>
+          <t>**Extended Data Fig. 3 | Representation comparison details.** Participants and conditions as in Fig. 3. **a**, Native heads by route (top) and per-condition gain from adding the retina or clinical data (bottom). #, label encoder inputs may define. **b**, BRAN combined minus 13 arms per condition under one fixed logistic readout (C = 1). Wins and losses, intervals excluding zero. **c**, The 14 arms of that readout. Ticks, one-sided Bonferroni bounds over five prespecified comparators. **d**, BRAN combined minus three arms under four readouts (¶, earlier label-free encoder), and earlier eye-alone AUROC (§, point estimates) beside tuned eye-alone contrasts. **e**, Paired differences with the fixed readout refitted on 25 to 100% of labels. Bars, within-fold participant bootstrap 95% intervals (1,000 draws), unadjusted per condition. BRAN combined did not exceed its clinical route, blood tests plus age or raw clinical values plus age (**c**), losing 7, 6 and 7 conditions to them (**b**). Adding the retina lowered heart-attack detection (**a**). The label-free encoder tied raw concatenation under tuned logistic and lost to ExtraTrees, and the retinal route trailed retinal foundation models (**d**). The clinical route beat BRAN combined at 50% and 75% of labels, and raw clinical values plus age beat it at 75% and scored higher at every budget (**e**). Per-arm tuning turned 125 wins and 0 losses against eight foundation-model arms into 76 and 16 (Fig. 3d). No panel is external validation. The Labrador cache discrepancy reaches 0.0054 AUROC per condition. Intervals for mean rows (**b**) and the 22-condition mean (**a**) are PLACEHOLDER.</t>
         </is>
       </c>
     </row>
